--- a/data/trans_orig/P1418-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2007</t>
+          <t>Población con diagnóstico de mala circulación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>16050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36428</t>
+          <t>34067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>32733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60563</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441284</t>
+          <t>443879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460958</t>
+          <t>460708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270252</t>
+          <t>272613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290287</t>
+          <t>290630</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719894</t>
+          <t>721085</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>746819</t>
+          <t>747724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27447</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>13061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>32060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28095</t>
+          <t>27049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51435</t>
+          <t>51825</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339487</t>
+          <t>338302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356069</t>
+          <t>355311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340047</t>
+          <t>339805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357797</t>
+          <t>358804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687364</t>
+          <t>686974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710704</t>
+          <t>711750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44036</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>35253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62599</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498353</t>
+          <t>499226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520972</t>
+          <t>521079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140852</t>
+          <t>140804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157209</t>
+          <t>157079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647572</t>
+          <t>645872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675564</t>
+          <t>674918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67926</t>
+          <t>66852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102027</t>
+          <t>99862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44628</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74317</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119067</t>
+          <t>118013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162263</t>
+          <t>162213</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1136307</t>
+          <t>1138472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1170408</t>
+          <t>1171482</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639968</t>
+          <t>642159</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>669657</t>
+          <t>671426</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1790357</t>
+          <t>1790407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1833553</t>
+          <t>1834607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16274</t>
+          <t>16440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36662</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>50285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81799</t>
+          <t>81162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72882</t>
+          <t>72041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109155</t>
+          <t>107613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>313893</t>
+          <t>314283</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334281</t>
+          <t>334115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>486953</t>
+          <t>487590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>518699</t>
+          <t>518467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>810152</t>
+          <t>811694</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>846425</t>
+          <t>847266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>137531</t>
+          <t>133068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182782</t>
+          <t>182073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141564</t>
+          <t>138017</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187358</t>
+          <t>185355</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290974</t>
+          <t>289828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1065978</t>
+          <t>1066687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1111229</t>
+          <t>1115692</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1359602</t>
+          <t>1361605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1405396</t>
+          <t>1408943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155265</t>
+          <t>155524</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205913</t>
+          <t>207429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>310079</t>
+          <t>309573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381432</t>
+          <t>378713</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>480797</t>
+          <t>481590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>563985</t>
+          <t>568657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3064277</t>
+          <t>3062761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3114925</t>
+          <t>3114666</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2996692</t>
+          <t>2999411</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3068045</t>
+          <t>3068551</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6084329</t>
+          <t>6079657</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6167517</t>
+          <t>6166724</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2012</t>
+          <t>Población con diagnóstico de mala circulación en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14395</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19574</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426904</t>
+          <t>426677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436185</t>
+          <t>435228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300059</t>
+          <t>300187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311228</t>
+          <t>311157</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732091</t>
+          <t>732274</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745622</t>
+          <t>745605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16213</t>
+          <t>15982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402584</t>
+          <t>402815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415751</t>
+          <t>415732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310871</t>
+          <t>312045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328642</t>
+          <t>328497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720171</t>
+          <t>720776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>741670</t>
+          <t>741646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12843</t>
+          <t>12740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40809</t>
+          <t>42629</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>36286</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>66067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596500</t>
+          <t>597402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>616572</t>
+          <t>616675</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219320</t>
+          <t>217500</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240492</t>
+          <t>239713</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>823179</t>
+          <t>823477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>852878</t>
+          <t>853258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41103</t>
+          <t>39652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>71324</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37924</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67799</t>
+          <t>67462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>87103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126049</t>
+          <t>130685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1086884</t>
+          <t>1087685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1117906</t>
+          <t>1119357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696923</t>
+          <t>697260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>726798</t>
+          <t>726114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1797682</t>
+          <t>1793046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1839905</t>
+          <t>1836628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,47%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10796</t>
+          <t>10833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27822</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81394</t>
+          <t>83440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120041</t>
+          <t>120942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99577</t>
+          <t>100215</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140255</t>
+          <t>143458</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482422</t>
+          <t>482774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499800</t>
+          <t>499763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>640205</t>
+          <t>639304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>678852</t>
+          <t>676806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1130588</t>
+          <t>1127385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1171266</t>
+          <t>1170628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>119904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165031</t>
+          <t>164593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>121827</t>
+          <t>123538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169579</t>
+          <t>169308</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259280</t>
+          <t>258430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265973</t>
+          <t>265971</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>943274</t>
+          <t>943712</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>990436</t>
+          <t>988401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1205608</t>
+          <t>1205879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1253360</t>
+          <t>1251649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85619</t>
+          <t>85112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128527</t>
+          <t>128000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>305843</t>
+          <t>311537</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>378501</t>
+          <t>383041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>409683</t>
+          <t>409709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>492129</t>
+          <t>496885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3293383</t>
+          <t>3293910</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3336291</t>
+          <t>3336798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3167367</t>
+          <t>3162827</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3240025</t>
+          <t>3234331</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6475649</t>
+          <t>6470893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6558095</t>
+          <t>6558069</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2016</t>
+          <t>Población con diagnóstico de mala circulación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413070</t>
+          <t>413675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425679</t>
+          <t>425992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323703</t>
+          <t>324123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>339204</t>
+          <t>340009</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743013</t>
+          <t>743006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762767</t>
+          <t>761791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>761</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369654</t>
+          <t>369794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377227</t>
+          <t>376466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>356387</t>
+          <t>355572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368917</t>
+          <t>369119</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730119</t>
+          <t>730608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744092</t>
+          <t>744370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15923</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35762</t>
+          <t>36056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503899</t>
+          <t>503699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517053</t>
+          <t>516777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142026</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158150</t>
+          <t>158382</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652274</t>
+          <t>651980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>672113</t>
+          <t>673478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21072</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44618</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26764</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52580</t>
+          <t>52633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>55073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88349</t>
+          <t>88993</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1105020</t>
+          <t>1105759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1128566</t>
+          <t>1128452</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>773296</t>
+          <t>773243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>799112</t>
+          <t>798284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1887165</t>
+          <t>1886521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1920451</t>
+          <t>1920441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21479</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42104</t>
+          <t>40919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>55664</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>89487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>83535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123318</t>
+          <t>121788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>578602</t>
+          <t>579787</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>599227</t>
+          <t>599856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>647842</t>
+          <t>648757</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682700</t>
+          <t>682580</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1235632</t>
+          <t>1237162</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1274994</t>
+          <t>1275415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87748</t>
+          <t>86976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127188</t>
+          <t>131366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84637</t>
+          <t>84935</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127977</t>
+          <t>127966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>954837</t>
+          <t>950659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>994277</t>
+          <t>995049</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1241193</t>
+          <t>1241204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1284533</t>
+          <t>1284235</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66949</t>
+          <t>65071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100838</t>
+          <t>100052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>220616</t>
+          <t>222210</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287076</t>
+          <t>285348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>299351</t>
+          <t>296503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370880</t>
+          <t>374403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3284884</t>
+          <t>3285670</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3318773</t>
+          <t>3320651</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3244520</t>
+          <t>3246248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3310980</t>
+          <t>3309386</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6546438</t>
+          <t>6542915</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6617967</t>
+          <t>6620815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2023</t>
+          <t>Población con diagnóstico de mala circulación en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>16405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27057</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481914</t>
+          <t>481286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496806</t>
+          <t>496468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>413620</t>
+          <t>412984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429809</t>
+          <t>429646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>901879</t>
+          <t>901657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924207</t>
+          <t>923491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23015</t>
+          <t>22813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42616</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>434377</t>
+          <t>433821</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445262</t>
+          <t>445296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350918</t>
+          <t>351148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367407</t>
+          <t>367852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>790452</t>
+          <t>789556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810053</t>
+          <t>810255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>70826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628686</t>
+          <t>625744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>660544</t>
+          <t>659293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134143</t>
+          <t>134116</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148378</t>
+          <t>148294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>763905</t>
+          <t>763630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814810</t>
+          <t>814203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73866</t>
+          <t>74038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71513</t>
+          <t>72179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76383</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>135850</t>
+          <t>134197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>959809</t>
+          <t>959637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>986512</t>
+          <t>986489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904850</t>
+          <t>904184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950374</t>
+          <t>950784</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1874188</t>
+          <t>1875841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1933655</t>
+          <t>1930672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34838</t>
+          <t>33723</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79184</t>
+          <t>80791</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133144</t>
+          <t>129322</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>106531</t>
+          <t>105647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157546</t>
+          <t>155412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>437889</t>
+          <t>439004</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455300</t>
+          <t>456105</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>704029</t>
+          <t>707851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>757989</t>
+          <t>756382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1152354</t>
+          <t>1154488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1203369</t>
+          <t>1204253</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79814</t>
+          <t>79774</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60743</t>
+          <t>59342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>88346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219003</t>
+          <t>220813</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239994</t>
+          <t>239985</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>680579</t>
+          <t>680619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>703844</t>
+          <t>704052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>911942</t>
+          <t>912554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>940157</t>
+          <t>941558</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104008</t>
+          <t>104012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160834</t>
+          <t>160661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>233935</t>
+          <t>244637</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>332518</t>
+          <t>333610</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>368759</t>
+          <t>370192</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>477158</t>
+          <t>475688</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3209990</t>
+          <t>3210163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3266816</t>
+          <t>3266812</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3236284</t>
+          <t>3235192</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3334867</t>
+          <t>3324165</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6462468</t>
+          <t>6463938</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6570867</t>
+          <t>6569434</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1418-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13068</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>36140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32733</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59372</t>
+          <t>59068</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443879</t>
+          <t>442999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>460708</t>
+          <t>460637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272613</t>
+          <t>270540</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290630</t>
+          <t>290338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>721085</t>
+          <t>721389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>747724</t>
+          <t>747570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28632</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32060</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27049</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51825</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338302</t>
+          <t>339904</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>355311</t>
+          <t>356238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339805</t>
+          <t>340210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358804</t>
+          <t>358239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686974</t>
+          <t>687801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711750</t>
+          <t>711116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>44552</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>27149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35253</t>
+          <t>35751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64299</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499226</t>
+          <t>497837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521079</t>
+          <t>520404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140804</t>
+          <t>140633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157079</t>
+          <t>157271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645872</t>
+          <t>647119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>674918</t>
+          <t>674420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66852</t>
+          <t>65345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>100695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42859</t>
+          <t>44462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>72241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118013</t>
+          <t>118026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162213</t>
+          <t>162583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1138472</t>
+          <t>1137639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1171482</t>
+          <t>1172989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642159</t>
+          <t>642044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671426</t>
+          <t>669823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1790407</t>
+          <t>1790037</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1834607</t>
+          <t>1834594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>36086</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50285</t>
+          <t>50545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81162</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72041</t>
+          <t>73208</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107613</t>
+          <t>108895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314283</t>
+          <t>314469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>334115</t>
+          <t>334316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>487590</t>
+          <t>488500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>518467</t>
+          <t>518207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>811694</t>
+          <t>810412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>847266</t>
+          <t>846099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>7361</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133068</t>
+          <t>134781</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182073</t>
+          <t>180705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>138017</t>
+          <t>139691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>185355</t>
+          <t>187481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>289828</t>
+          <t>290840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297385</t>
+          <t>297378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1066687</t>
+          <t>1068055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1115692</t>
+          <t>1113979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1361605</t>
+          <t>1359479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1408943</t>
+          <t>1407269</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155524</t>
+          <t>155222</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207429</t>
+          <t>204573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>309573</t>
+          <t>308666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>378713</t>
+          <t>382930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>481590</t>
+          <t>476480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>568657</t>
+          <t>567485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3062761</t>
+          <t>3065617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3114666</t>
+          <t>3114968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2999411</t>
+          <t>2995194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3068551</t>
+          <t>3069458</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6079657</t>
+          <t>6080829</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6166724</t>
+          <t>6171834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>13597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6060</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>426677</t>
+          <t>427916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435228</t>
+          <t>436195</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300187</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311157</t>
+          <t>311443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>732274</t>
+          <t>730885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745605</t>
+          <t>745694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9514</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402815</t>
+          <t>402823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415732</t>
+          <t>415785</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312045</t>
+          <t>311929</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328497</t>
+          <t>327957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>720776</t>
+          <t>719514</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>741646</t>
+          <t>742002</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>31915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42629</t>
+          <t>42007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36286</t>
+          <t>36783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66067</t>
+          <t>65734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597402</t>
+          <t>597500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>616675</t>
+          <t>617193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217500</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239713</t>
+          <t>240880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>823477</t>
+          <t>823810</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>853258</t>
+          <t>852761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>39143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71324</t>
+          <t>70271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67462</t>
+          <t>67485</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87103</t>
+          <t>83734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130685</t>
+          <t>126115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1087685</t>
+          <t>1088738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1119357</t>
+          <t>1119866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697260</t>
+          <t>697237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>726114</t>
+          <t>726876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1793046</t>
+          <t>1797616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1836628</t>
+          <t>1839997</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83440</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>120942</t>
+          <t>121843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100215</t>
+          <t>97252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143458</t>
+          <t>139912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>482774</t>
+          <t>483467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499763</t>
+          <t>499964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>639304</t>
+          <t>638403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>676806</t>
+          <t>676858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1127385</t>
+          <t>1130931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1170628</t>
+          <t>1173591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119904</t>
+          <t>119923</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>164593</t>
+          <t>165755</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123538</t>
+          <t>122045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169308</t>
+          <t>169191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258430</t>
+          <t>259276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265971</t>
+          <t>265970</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>943712</t>
+          <t>942550</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>988401</t>
+          <t>988382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1205879</t>
+          <t>1205996</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1251649</t>
+          <t>1253142</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85112</t>
+          <t>89382</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128000</t>
+          <t>130295</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>311537</t>
+          <t>306717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383041</t>
+          <t>381793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>409709</t>
+          <t>411159</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>496885</t>
+          <t>492480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3293910</t>
+          <t>3291615</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3336798</t>
+          <t>3332528</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3162827</t>
+          <t>3164075</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3234331</t>
+          <t>3239151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6470893</t>
+          <t>6475298</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6558069</t>
+          <t>6556619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15417</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413675</t>
+          <t>413271</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>425992</t>
+          <t>425524</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>324123</t>
+          <t>323515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340009</t>
+          <t>339395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>743006</t>
+          <t>741252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>761791</t>
+          <t>762372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>15883</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369794</t>
+          <t>370506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376466</t>
+          <t>376464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>355572</t>
+          <t>356390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369119</t>
+          <t>368924</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730608</t>
+          <t>729450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744370</t>
+          <t>743820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>18523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23106</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36056</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503699</t>
+          <t>503391</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516777</t>
+          <t>516713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143017</t>
+          <t>144053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158382</t>
+          <t>158591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>651980</t>
+          <t>652013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673478</t>
+          <t>672534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43879</t>
+          <t>44928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27592</t>
+          <t>27794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52633</t>
+          <t>52928</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55073</t>
+          <t>54501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88993</t>
+          <t>88120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1105759</t>
+          <t>1104710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1128452</t>
+          <t>1127917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>773243</t>
+          <t>772948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>798284</t>
+          <t>798082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886521</t>
+          <t>1887394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1920441</t>
+          <t>1921013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40919</t>
+          <t>40703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55664</t>
+          <t>56016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89487</t>
+          <t>88692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83535</t>
+          <t>82230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121788</t>
+          <t>122452</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>579787</t>
+          <t>580003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>599856</t>
+          <t>600812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>648757</t>
+          <t>649552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>682580</t>
+          <t>682228</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1237162</t>
+          <t>1236498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1275415</t>
+          <t>1276720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86976</t>
+          <t>84922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>131366</t>
+          <t>129123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84935</t>
+          <t>87023</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127966</t>
+          <t>130578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>950659</t>
+          <t>952902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>995049</t>
+          <t>997103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1241204</t>
+          <t>1238592</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1284235</t>
+          <t>1282147</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65071</t>
+          <t>64858</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100052</t>
+          <t>100074</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>222210</t>
+          <t>220409</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>285348</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>296503</t>
+          <t>297400</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>374403</t>
+          <t>372884</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3285670</t>
+          <t>3285648</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3320651</t>
+          <t>3320864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3246248</t>
+          <t>3245855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3309386</t>
+          <t>3311187</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6542915</t>
+          <t>6544434</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6620815</t>
+          <t>6619918</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14209</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8744</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23926</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23481</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,17 +8703,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>41125</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>30551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49607</t>
+          <t>53611</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>491003</t>
+          <t>535067</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>481286</t>
+          <t>526746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496468</t>
+          <t>541666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>422570</t>
+          <t>461410</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412984</t>
+          <t>450659</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>429646</t>
+          <t>468765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,17 +8816,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>913574</t>
+          <t>996477</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>901657</t>
+          <t>983991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>923491</t>
+          <t>1007051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446051</t>
+          <t>486984</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446051</t>
+          <t>486984</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446051</t>
+          <t>486984</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>1037602</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>1037602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951264</t>
+          <t>1037602</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10512</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30763</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>31315</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>47586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>440644</t>
+          <t>470265</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433821</t>
+          <t>463016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>445296</t>
+          <t>475067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>361108</t>
+          <t>398460</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351148</t>
+          <t>388713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367852</t>
+          <t>406584</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>801753</t>
+          <t>868725</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>789556</t>
+          <t>857022</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>810255</t>
+          <t>878302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451156</t>
+          <t>482116</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451156</t>
+          <t>482116</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451156</t>
+          <t>482116</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833068</t>
+          <t>904608</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833068</t>
+          <t>904608</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833068</t>
+          <t>904608</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24738</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46833</t>
+          <t>51384</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70826</t>
+          <t>63264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645450</t>
+          <t>447830</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625744</t>
+          <t>437079</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659293</t>
+          <t>455462</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>142173</t>
+          <t>159026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134116</t>
+          <t>149636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148294</t>
+          <t>166247</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>787623</t>
+          <t>606857</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>763630</t>
+          <t>594977</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814203</t>
+          <t>618625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60117</t>
+          <t>66386</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74038</t>
+          <t>83271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>58144</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72179</t>
+          <t>70632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>113224</t>
+          <t>124530</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>106571</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134197</t>
+          <t>144999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>973558</t>
+          <t>1064324</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>959637</t>
+          <t>1047439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>986489</t>
+          <t>1077292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>923256</t>
+          <t>800152</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904184</t>
+          <t>787664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>950784</t>
+          <t>810092</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1896814</t>
+          <t>1864476</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1875841</t>
+          <t>1844007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1930672</t>
+          <t>1882435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033675</t>
+          <t>1130710</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033675</t>
+          <t>1130710</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033675</t>
+          <t>1130710</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>976363</t>
+          <t>858296</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>976363</t>
+          <t>858296</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>976363</t>
+          <t>858296</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010038</t>
+          <t>1989006</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010038</t>
+          <t>1989006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010038</t>
+          <t>1989006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33723</t>
+          <t>36374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>108286</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80791</t>
+          <t>99228</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>129322</t>
+          <t>127829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>132765</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105647</t>
+          <t>121598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155412</t>
+          <t>158497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>448248</t>
+          <t>539927</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439004</t>
+          <t>529204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456105</t>
+          <t>547633</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>728887</t>
+          <t>715758</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>707851</t>
+          <t>700248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756382</t>
+          <t>728849</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1177135</t>
+          <t>1255685</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1154488</t>
+          <t>1235158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1204253</t>
+          <t>1272057</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472727</t>
+          <t>565578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>837173</t>
+          <t>828077</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>837173</t>
+          <t>828077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>837173</t>
+          <t>828077</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1309900</t>
+          <t>1393655</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309900</t>
+          <t>1393655</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1309900</t>
+          <t>1393655</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,22 +10348,22 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19694</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>67458</t>
+          <t>75102</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>63560</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79774</t>
+          <t>90168</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72291</t>
+          <t>79518</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59342</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88346</t>
+          <t>97460</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235673</t>
+          <t>232812</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220813</t>
+          <t>218747</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239985</t>
+          <t>236710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>692935</t>
+          <t>768209</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>680619</t>
+          <t>753143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>704052</t>
+          <t>779751</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>928609</t>
+          <t>1001021</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>912554</t>
+          <t>983079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>941558</t>
+          <t>1015682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760393</t>
+          <t>843311</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760393</t>
+          <t>843311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760393</t>
+          <t>843311</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000900</t>
+          <t>1080539</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000900</t>
+          <t>1080539</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000900</t>
+          <t>1080539</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>136247</t>
+          <t>146768</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104012</t>
+          <t>125048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160661</t>
+          <t>169145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>297872</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>244637</t>
+          <t>296073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>333610</t>
+          <t>352918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>434119</t>
+          <t>470409</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>370192</t>
+          <t>434064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>475688</t>
+          <t>504462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3234577</t>
+          <t>3290225</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3210163</t>
+          <t>3267848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3266812</t>
+          <t>3311945</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3270930</t>
+          <t>3303015</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3235192</t>
+          <t>3273739</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3324165</t>
+          <t>3330584</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6505507</t>
+          <t>6593241</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6463938</t>
+          <t>6559188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6569434</t>
+          <t>6629586</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370824</t>
+          <t>3436993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370824</t>
+          <t>3436993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370824</t>
+          <t>3436993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3568802</t>
+          <t>3626657</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3568802</t>
+          <t>3626657</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3568802</t>
+          <t>3626657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6939626</t>
+          <t>7063650</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6939626</t>
+          <t>7063650</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6939626</t>
+          <t>7063650</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
